--- a/product-definitions/spreadsheet/mean-winds-profile.xlsx
+++ b/product-definitions/spreadsheet/mean-winds-profile.xlsx
@@ -3,14 +3,31 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="dimensions-specific" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="variables-specific" sheetId="2" r:id="rId4"/>
+    <sheet state="visible" name="dimensions-specific" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="variables-specific" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="D114">
+      <text>
+        <t xml:space="preserve">@joshua.hampton@ncas.ac.uk  - we need to gather these standard names and start the process of getting them through CF
+_Assigned to joshua.hampton@ncas.ac.uk_
+	-Graham Parton</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="68">
   <si>
@@ -140,7 +157,7 @@
     <t>Wind From Direction</t>
   </si>
   <si>
-    <t>wind_speed_of_gust_from_direction</t>
+    <t>wind_gust_from_direction</t>
   </si>
   <si>
     <t>Direction of Maximum Wind Speed Observed in Averaging Period</t>
@@ -219,8 +236,8 @@
 good_data
 bad_data_data_values_outside_measurement_range
 bad_data_signal_below_instrument _threshold
-suspect_data_line_of_sight_radial_velocity_ -19m_s-1_&lt;&gt; _19m_s-1
-suspect_data_line_of_sight_radial_velocity_wind_shear_-5m_s-1_&lt;&gt;_5m_s-1
+suspect_data_line_of_sight_radial_velocity_ less_than_-19m_s-1_or_greater_than _19m_s-1
+suspect_data_line_of_sight_radial_velocity_wind_shear_less_than_-5m_s-1_or_greater_than_5m_s-1
 suspect_data_instrument_internal_temperature_outside_operational_range_low _(15C)
 suspect_data_Instrument_internal_temperature_outside_operational_range_high_(40C)
 bad_data_gate_index_exceeds_number_of_measurement_gates_in_use
@@ -231,7 +248,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="8">
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -249,9 +272,16 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -283,80 +313,76 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -375,17 +401,211 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="18.14"/>
-    <col customWidth="1" min="3" max="3" width="45.57"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.88"/>
+    <col customWidth="1" min="3" max="3" width="39.88"/>
+    <col customWidth="1" min="4" max="23" width="7.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
@@ -418,9 +638,6 @@
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
@@ -452,9 +669,6 @@
       <c r="U2" s="3"/>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="12.0" customHeight="1">
       <c r="A3" s="5"/>
@@ -480,9 +694,6 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
     </row>
     <row r="4" ht="12.0" customHeight="1">
       <c r="A4" s="5"/>
@@ -508,9 +719,6 @@
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
     </row>
     <row r="5" ht="12.0" customHeight="1"/>
     <row r="6" ht="12.0" customHeight="1"/>
@@ -728,786 +936,786 @@
     <row r="218" ht="12.0" customHeight="1"/>
     <row r="219" ht="12.0" customHeight="1"/>
     <row r="220" ht="12.0" customHeight="1"/>
-    <row r="221" ht="12.0" customHeight="1"/>
-    <row r="222" ht="12.0" customHeight="1"/>
-    <row r="223" ht="12.0" customHeight="1"/>
-    <row r="224" ht="12.0" customHeight="1"/>
-    <row r="225" ht="12.0" customHeight="1"/>
-    <row r="226" ht="12.0" customHeight="1"/>
-    <row r="227" ht="12.0" customHeight="1"/>
-    <row r="228" ht="12.0" customHeight="1"/>
-    <row r="229" ht="12.0" customHeight="1"/>
-    <row r="230" ht="12.0" customHeight="1"/>
-    <row r="231" ht="12.0" customHeight="1"/>
-    <row r="232" ht="12.0" customHeight="1"/>
-    <row r="233" ht="12.0" customHeight="1"/>
-    <row r="234" ht="12.0" customHeight="1"/>
-    <row r="235" ht="12.0" customHeight="1"/>
-    <row r="236" ht="12.0" customHeight="1"/>
-    <row r="237" ht="12.0" customHeight="1"/>
-    <row r="238" ht="12.0" customHeight="1"/>
-    <row r="239" ht="12.0" customHeight="1"/>
-    <row r="240" ht="12.0" customHeight="1"/>
-    <row r="241" ht="12.0" customHeight="1"/>
-    <row r="242" ht="12.0" customHeight="1"/>
-    <row r="243" ht="12.0" customHeight="1"/>
-    <row r="244" ht="12.0" customHeight="1"/>
-    <row r="245" ht="12.0" customHeight="1"/>
-    <row r="246" ht="12.0" customHeight="1"/>
-    <row r="247" ht="12.0" customHeight="1"/>
-    <row r="248" ht="12.0" customHeight="1"/>
-    <row r="249" ht="12.0" customHeight="1"/>
-    <row r="250" ht="12.0" customHeight="1"/>
-    <row r="251" ht="12.0" customHeight="1"/>
-    <row r="252" ht="12.0" customHeight="1"/>
-    <row r="253" ht="12.0" customHeight="1"/>
-    <row r="254" ht="12.0" customHeight="1"/>
-    <row r="255" ht="12.0" customHeight="1"/>
-    <row r="256" ht="12.0" customHeight="1"/>
-    <row r="257" ht="12.0" customHeight="1"/>
-    <row r="258" ht="12.0" customHeight="1"/>
-    <row r="259" ht="12.0" customHeight="1"/>
-    <row r="260" ht="12.0" customHeight="1"/>
-    <row r="261" ht="12.0" customHeight="1"/>
-    <row r="262" ht="12.0" customHeight="1"/>
-    <row r="263" ht="12.0" customHeight="1"/>
-    <row r="264" ht="12.0" customHeight="1"/>
-    <row r="265" ht="12.0" customHeight="1"/>
-    <row r="266" ht="12.0" customHeight="1"/>
-    <row r="267" ht="12.0" customHeight="1"/>
-    <row r="268" ht="12.0" customHeight="1"/>
-    <row r="269" ht="12.0" customHeight="1"/>
-    <row r="270" ht="12.0" customHeight="1"/>
-    <row r="271" ht="12.0" customHeight="1"/>
-    <row r="272" ht="12.0" customHeight="1"/>
-    <row r="273" ht="12.0" customHeight="1"/>
-    <row r="274" ht="12.0" customHeight="1"/>
-    <row r="275" ht="12.0" customHeight="1"/>
-    <row r="276" ht="12.0" customHeight="1"/>
-    <row r="277" ht="12.0" customHeight="1"/>
-    <row r="278" ht="12.0" customHeight="1"/>
-    <row r="279" ht="12.0" customHeight="1"/>
-    <row r="280" ht="12.0" customHeight="1"/>
-    <row r="281" ht="12.0" customHeight="1"/>
-    <row r="282" ht="12.0" customHeight="1"/>
-    <row r="283" ht="12.0" customHeight="1"/>
-    <row r="284" ht="12.0" customHeight="1"/>
-    <row r="285" ht="12.0" customHeight="1"/>
-    <row r="286" ht="12.0" customHeight="1"/>
-    <row r="287" ht="12.0" customHeight="1"/>
-    <row r="288" ht="12.0" customHeight="1"/>
-    <row r="289" ht="12.0" customHeight="1"/>
-    <row r="290" ht="12.0" customHeight="1"/>
-    <row r="291" ht="12.0" customHeight="1"/>
-    <row r="292" ht="12.0" customHeight="1"/>
-    <row r="293" ht="12.0" customHeight="1"/>
-    <row r="294" ht="12.0" customHeight="1"/>
-    <row r="295" ht="12.0" customHeight="1"/>
-    <row r="296" ht="12.0" customHeight="1"/>
-    <row r="297" ht="12.0" customHeight="1"/>
-    <row r="298" ht="12.0" customHeight="1"/>
-    <row r="299" ht="12.0" customHeight="1"/>
-    <row r="300" ht="12.0" customHeight="1"/>
-    <row r="301" ht="12.0" customHeight="1"/>
-    <row r="302" ht="12.0" customHeight="1"/>
-    <row r="303" ht="12.0" customHeight="1"/>
-    <row r="304" ht="12.0" customHeight="1"/>
-    <row r="305" ht="12.0" customHeight="1"/>
-    <row r="306" ht="12.0" customHeight="1"/>
-    <row r="307" ht="12.0" customHeight="1"/>
-    <row r="308" ht="12.0" customHeight="1"/>
-    <row r="309" ht="12.0" customHeight="1"/>
-    <row r="310" ht="12.0" customHeight="1"/>
-    <row r="311" ht="12.0" customHeight="1"/>
-    <row r="312" ht="12.0" customHeight="1"/>
-    <row r="313" ht="12.0" customHeight="1"/>
-    <row r="314" ht="12.0" customHeight="1"/>
-    <row r="315" ht="12.0" customHeight="1"/>
-    <row r="316" ht="12.0" customHeight="1"/>
-    <row r="317" ht="12.0" customHeight="1"/>
-    <row r="318" ht="12.0" customHeight="1"/>
-    <row r="319" ht="12.0" customHeight="1"/>
-    <row r="320" ht="12.0" customHeight="1"/>
-    <row r="321" ht="12.0" customHeight="1"/>
-    <row r="322" ht="12.0" customHeight="1"/>
-    <row r="323" ht="12.0" customHeight="1"/>
-    <row r="324" ht="12.0" customHeight="1"/>
-    <row r="325" ht="12.0" customHeight="1"/>
-    <row r="326" ht="12.0" customHeight="1"/>
-    <row r="327" ht="12.0" customHeight="1"/>
-    <row r="328" ht="12.0" customHeight="1"/>
-    <row r="329" ht="12.0" customHeight="1"/>
-    <row r="330" ht="12.0" customHeight="1"/>
-    <row r="331" ht="12.0" customHeight="1"/>
-    <row r="332" ht="12.0" customHeight="1"/>
-    <row r="333" ht="12.0" customHeight="1"/>
-    <row r="334" ht="12.0" customHeight="1"/>
-    <row r="335" ht="12.0" customHeight="1"/>
-    <row r="336" ht="12.0" customHeight="1"/>
-    <row r="337" ht="12.0" customHeight="1"/>
-    <row r="338" ht="12.0" customHeight="1"/>
-    <row r="339" ht="12.0" customHeight="1"/>
-    <row r="340" ht="12.0" customHeight="1"/>
-    <row r="341" ht="12.0" customHeight="1"/>
-    <row r="342" ht="12.0" customHeight="1"/>
-    <row r="343" ht="12.0" customHeight="1"/>
-    <row r="344" ht="12.0" customHeight="1"/>
-    <row r="345" ht="12.0" customHeight="1"/>
-    <row r="346" ht="12.0" customHeight="1"/>
-    <row r="347" ht="12.0" customHeight="1"/>
-    <row r="348" ht="12.0" customHeight="1"/>
-    <row r="349" ht="12.0" customHeight="1"/>
-    <row r="350" ht="12.0" customHeight="1"/>
-    <row r="351" ht="12.0" customHeight="1"/>
-    <row r="352" ht="12.0" customHeight="1"/>
-    <row r="353" ht="12.0" customHeight="1"/>
-    <row r="354" ht="12.0" customHeight="1"/>
-    <row r="355" ht="12.0" customHeight="1"/>
-    <row r="356" ht="12.0" customHeight="1"/>
-    <row r="357" ht="12.0" customHeight="1"/>
-    <row r="358" ht="12.0" customHeight="1"/>
-    <row r="359" ht="12.0" customHeight="1"/>
-    <row r="360" ht="12.0" customHeight="1"/>
-    <row r="361" ht="12.0" customHeight="1"/>
-    <row r="362" ht="12.0" customHeight="1"/>
-    <row r="363" ht="12.0" customHeight="1"/>
-    <row r="364" ht="12.0" customHeight="1"/>
-    <row r="365" ht="12.0" customHeight="1"/>
-    <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
-    <row r="994" ht="12.0" customHeight="1"/>
-    <row r="995" ht="12.0" customHeight="1"/>
-    <row r="996" ht="12.0" customHeight="1"/>
-    <row r="997" ht="12.0" customHeight="1"/>
-    <row r="998" ht="12.0" customHeight="1"/>
-    <row r="999" ht="12.0" customHeight="1"/>
-    <row r="1000" ht="12.0" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1518,14 +1726,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="17.86"/>
-    <col customWidth="1" min="3" max="3" width="26.71"/>
-    <col customWidth="1" min="4" max="5" width="17.86"/>
-    <col customWidth="1" min="6" max="6" width="17.57"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.63"/>
+    <col customWidth="1" min="3" max="3" width="23.38"/>
+    <col customWidth="1" min="4" max="5" width="15.63"/>
+    <col customWidth="1" min="6" max="6" width="15.38"/>
+    <col customWidth="1" min="7" max="16" width="7.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
@@ -1549,13 +1757,13 @@
       </c>
     </row>
     <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" t="s">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="9"/>
+      <c r="C2" s="10"/>
     </row>
     <row r="3" ht="12.0" customHeight="1">
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
@@ -1563,7 +1771,7 @@
       </c>
     </row>
     <row r="4" ht="12.0" customHeight="1">
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -1571,31 +1779,31 @@
       </c>
     </row>
     <row r="5" ht="12.0" customHeight="1">
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="12.0" customHeight="1">
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" ht="12.0" customHeight="1">
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" ht="12.0" customHeight="1">
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="12">
@@ -1603,10 +1811,10 @@
       </c>
     </row>
     <row r="9" ht="12.0" customHeight="1">
-      <c r="B9" t="s">
+      <c r="B9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1663,7 +1871,7 @@
       <c r="B15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="13"/>
@@ -1713,7 +1921,7 @@
       <c r="B20" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D20" s="13"/>
@@ -1723,7 +1931,7 @@
       <c r="B21" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="13"/>
@@ -1733,7 +1941,7 @@
       <c r="B22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="13"/>
@@ -1777,7 +1985,7 @@
       <c r="B27" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D27" s="13"/>
@@ -1787,7 +1995,7 @@
       <c r="B28" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="13"/>
@@ -1827,7 +2035,7 @@
       <c r="B32" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D32" s="13"/>
@@ -1837,7 +2045,7 @@
       <c r="B33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D33" s="13"/>
@@ -1847,7 +2055,7 @@
       <c r="B34" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D34" s="13"/>
@@ -1879,7 +2087,7 @@
       <c r="D37" s="13"/>
       <c r="K37" s="13"/>
       <c r="L37" s="13"/>
-      <c r="M37" s="21"/>
+      <c r="M37" s="20"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
@@ -1897,7 +2105,7 @@
       <c r="H38" s="13"/>
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
-      <c r="M38" s="22"/>
+      <c r="M38" s="20"/>
       <c r="N38" s="13"/>
       <c r="O38" s="13"/>
       <c r="P38" s="13"/>
@@ -1907,7 +2115,7 @@
       <c r="B39" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="13"/>
@@ -1917,7 +2125,7 @@
       <c r="H39" s="13"/>
       <c r="K39" s="13"/>
       <c r="L39" s="13"/>
-      <c r="M39" s="23"/>
+      <c r="M39" s="21"/>
       <c r="N39" s="13"/>
       <c r="O39" s="13"/>
       <c r="P39" s="13"/>
@@ -1927,7 +2135,7 @@
       <c r="B40" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D40" s="13"/>
@@ -1937,7 +2145,7 @@
       <c r="H40" s="13"/>
       <c r="K40" s="13"/>
       <c r="L40" s="13"/>
-      <c r="M40" s="24"/>
+      <c r="M40" s="22"/>
       <c r="N40" s="13"/>
       <c r="O40" s="13"/>
       <c r="P40" s="13"/>
@@ -1977,7 +2185,7 @@
       <c r="H42" s="13"/>
       <c r="K42" s="13"/>
       <c r="L42" s="13"/>
-      <c r="M42" s="21"/>
+      <c r="M42" s="20"/>
       <c r="N42" s="13"/>
       <c r="O42" s="13"/>
       <c r="P42" s="13"/>
@@ -1997,7 +2205,7 @@
       <c r="H43" s="13"/>
       <c r="K43" s="13"/>
       <c r="L43" s="13"/>
-      <c r="M43" s="25"/>
+      <c r="M43" s="21"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13"/>
       <c r="P43" s="13"/>
@@ -2007,7 +2215,7 @@
       <c r="B44" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D44" s="13"/>
@@ -2016,8 +2224,8 @@
       <c r="G44" s="13"/>
       <c r="H44" s="13"/>
       <c r="K44" s="13"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="26"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="23"/>
       <c r="N44" s="13"/>
       <c r="O44" s="13"/>
       <c r="P44" s="13"/>
@@ -2027,7 +2235,7 @@
       <c r="B45" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D45" s="13"/>
@@ -2041,7 +2249,7 @@
       <c r="B46" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D46" s="13"/>
@@ -2073,7 +2281,7 @@
       <c r="D49" s="13"/>
     </row>
     <row r="50" ht="12.0" customHeight="1">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B50" s="13"/>
@@ -2095,7 +2303,7 @@
       <c r="B52" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D52" s="13"/>
@@ -2115,10 +2323,10 @@
       <c r="B54" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="15" t="s">
+      <c r="C54" s="25" t="s">
         <v>42</v>
       </c>
+      <c r="D54" s="15"/>
     </row>
     <row r="55" ht="12.0" customHeight="1">
       <c r="A55" s="13"/>
@@ -2135,7 +2343,7 @@
       <c r="B56" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D56" s="13"/>
@@ -2145,7 +2353,7 @@
       <c r="B57" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D57" s="13"/>
@@ -2155,7 +2363,7 @@
       <c r="B58" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D58" s="13"/>
@@ -2209,7 +2417,7 @@
       <c r="B64" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D64" s="13"/>
@@ -2249,7 +2457,7 @@
       <c r="B68" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="18">
+      <c r="C68" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D68" s="13"/>
@@ -2259,7 +2467,7 @@
       <c r="B69" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D69" s="13"/>
@@ -2269,7 +2477,7 @@
       <c r="B70" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D70" s="13"/>
@@ -2323,7 +2531,7 @@
       <c r="B76" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C76" s="20" t="s">
+      <c r="C76" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D76" s="13"/>
@@ -2363,7 +2571,7 @@
       <c r="B80" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="18">
+      <c r="C80" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D80" s="13"/>
@@ -2373,7 +2581,7 @@
       <c r="B81" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D81" s="13"/>
@@ -2383,7 +2591,7 @@
       <c r="B82" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D82" s="13"/>
@@ -2437,7 +2645,7 @@
       <c r="B88" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D88" s="13"/>
@@ -2477,7 +2685,7 @@
       <c r="B92" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D92" s="13"/>
@@ -2487,7 +2695,7 @@
       <c r="B93" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D93" s="13"/>
@@ -2497,7 +2705,7 @@
       <c r="B94" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C94" s="19" t="s">
+      <c r="C94" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D94" s="13"/>
@@ -2551,7 +2759,7 @@
       <c r="B100" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C100" s="20" t="s">
+      <c r="C100" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D100" s="13"/>
@@ -2581,7 +2789,7 @@
       <c r="B103" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C103" s="25" t="s">
+      <c r="C103" s="21" t="s">
         <v>51</v>
       </c>
       <c r="D103" s="13"/>
@@ -2591,7 +2799,7 @@
       <c r="B104" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="18">
+      <c r="C104" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D104" s="13"/>
@@ -2601,7 +2809,7 @@
       <c r="B105" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C105" s="19" t="s">
+      <c r="C105" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D105" s="13"/>
@@ -2611,7 +2819,7 @@
       <c r="B106" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D106" s="13"/>
@@ -2665,7 +2873,7 @@
       <c r="B112" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C112" s="20" t="s">
+      <c r="C112" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D112" s="13"/>
@@ -2695,7 +2903,7 @@
       <c r="B115" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C115" s="25" t="s">
+      <c r="C115" s="21" t="s">
         <v>54</v>
       </c>
       <c r="D115" s="13"/>
@@ -2705,7 +2913,7 @@
       <c r="B116" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D116" s="13"/>
@@ -2715,7 +2923,7 @@
       <c r="B117" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D117" s="13"/>
@@ -2725,7 +2933,7 @@
       <c r="B118" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="C118" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D118" s="13"/>
@@ -2785,7 +2993,7 @@
       <c r="B125" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C125" s="20" t="s">
+      <c r="C125" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D125" s="13"/>
@@ -2815,7 +3023,7 @@
       <c r="B128" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C128" s="25" t="s">
+      <c r="C128" s="21" t="s">
         <v>56</v>
       </c>
       <c r="D128" s="13"/>
@@ -2825,7 +3033,7 @@
       <c r="B129" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C129" s="18">
+      <c r="C129" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D129" s="13"/>
@@ -2835,7 +3043,7 @@
       <c r="B130" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C130" s="19" t="s">
+      <c r="C130" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D130" s="13"/>
@@ -2845,7 +3053,7 @@
       <c r="B131" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D131" s="13"/>
@@ -2899,7 +3107,7 @@
       <c r="B137" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C137" s="20" t="s">
+      <c r="C137" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D137" s="13"/>
@@ -2929,7 +3137,7 @@
       <c r="B140" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C140" s="25" t="s">
+      <c r="C140" s="21" t="s">
         <v>58</v>
       </c>
       <c r="D140" s="13"/>
@@ -2939,7 +3147,7 @@
       <c r="B141" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C141" s="18">
+      <c r="C141" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D141" s="13"/>
@@ -2949,7 +3157,7 @@
       <c r="B142" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="C142" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D142" s="13"/>
@@ -2959,7 +3167,7 @@
       <c r="B143" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C143" s="19" t="s">
+      <c r="C143" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D143" s="13"/>
@@ -3013,7 +3221,7 @@
       <c r="B149" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C149" s="20" t="s">
+      <c r="C149" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D149" s="13"/>
@@ -3043,7 +3251,7 @@
       <c r="B152" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C152" s="25" t="s">
+      <c r="C152" s="21" t="s">
         <v>60</v>
       </c>
       <c r="D152" s="13"/>
@@ -3053,7 +3261,7 @@
       <c r="B153" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C153" s="18">
+      <c r="C153" s="17">
         <v>-1.0E20</v>
       </c>
       <c r="D153" s="13"/>
@@ -3063,7 +3271,7 @@
       <c r="B154" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C154" s="19" t="s">
+      <c r="C154" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D154" s="13"/>
@@ -3073,7 +3281,7 @@
       <c r="B155" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C155" s="19" t="s">
+      <c r="C155" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D155" s="13"/>
@@ -3104,7 +3312,7 @@
         <v>61</v>
       </c>
       <c r="B159" s="13"/>
-      <c r="C159" s="21"/>
+      <c r="C159" s="20"/>
       <c r="D159" s="13"/>
       <c r="E159" s="13"/>
       <c r="F159" s="13"/>
@@ -3114,7 +3322,7 @@
       <c r="B160" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C160" s="22" t="s">
+      <c r="C160" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D160" s="13"/>
@@ -3126,7 +3334,7 @@
       <c r="B161" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C161" s="20" t="s">
+      <c r="C161" s="19" t="s">
         <v>30</v>
       </c>
       <c r="D161" s="13"/>
@@ -3138,7 +3346,7 @@
       <c r="B162" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C162" s="24">
+      <c r="C162" s="22">
         <v>1.0</v>
       </c>
       <c r="D162" s="13"/>
@@ -3160,7 +3368,7 @@
       <c r="B164" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C164" s="21" t="s">
+      <c r="C164" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D164" s="13"/>
@@ -3172,16 +3380,16 @@
       <c r="B165" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C165" s="25" t="s">
+      <c r="C165" s="21" t="s">
         <v>65</v>
       </c>
       <c r="D165" s="13"/>
       <c r="E165" s="13"/>
       <c r="F165" s="13"/>
     </row>
-    <row r="166" ht="12.0" customHeight="1">
+    <row r="166">
       <c r="A166" s="13"/>
-      <c r="B166" s="21" t="s">
+      <c r="B166" s="20" t="s">
         <v>66</v>
       </c>
       <c r="C166" s="26" t="s">
@@ -3391,638 +3599,642 @@
     <row r="364" ht="12.0" customHeight="1"/>
     <row r="365" ht="12.0" customHeight="1"/>
     <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
-    <row r="994" ht="12.0" customHeight="1"/>
-    <row r="995" ht="12.0" customHeight="1"/>
-    <row r="996" ht="12.0" customHeight="1"/>
-    <row r="997" ht="12.0" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/product-definitions/spreadsheet/mean-winds-profile.xlsx
+++ b/product-definitions/spreadsheet/mean-winds-profile.xlsx
@@ -248,7 +248,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -274,11 +274,6 @@
       <b/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
@@ -309,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -345,13 +340,13 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -363,8 +358,8 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -373,17 +368,8 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2281,7 +2267,7 @@
       <c r="D49" s="13"/>
     </row>
     <row r="50" ht="12.0" customHeight="1">
-      <c r="A50" s="24" t="s">
+      <c r="A50" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B50" s="13"/>
@@ -2323,7 +2309,7 @@
       <c r="B54" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D54" s="15"/>
@@ -3387,12 +3373,12 @@
       <c r="E165" s="13"/>
       <c r="F165" s="13"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="13"/>
       <c r="B166" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="C166" s="26" t="s">
+      <c r="C166" s="23" t="s">
         <v>67</v>
       </c>
       <c r="D166" s="13"/>
